--- a/Assignments/HW3/Fitness Band Experiment.xlsx
+++ b/Assignments/HW3/Fitness Band Experiment.xlsx
@@ -409,7 +409,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="3">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="F3">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>5.26</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="6">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="7">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="8">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>4.19</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>3.97</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="11">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>8.31</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>8.789999999999999</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>8.800000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
   </sheetData>
